--- a/ONCHO/Entomological survey Survey/Nigeria/2026/kaduna/ng_oncho_2609_4_b_lab_kad.xlsx
+++ b/ONCHO/Entomological survey Survey/Nigeria/2026/kaduna/ng_oncho_2609_4_b_lab_kad.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bonhe\Repositories\dsa-forms\ONCHO\Entomological survey Survey\Nigeria\2026\kaduna\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yumbad\Repositories\dsa-forms\ONCHO\Entomological survey Survey\Nigeria\2026\kaduna\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB64556D-2E0C-4F0B-A584-FB9351AB529A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D22CE3A-3BF4-45AD-B78B-B3B4DDCE5F81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="survey" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="131">
   <si>
     <t>type</t>
   </si>
@@ -413,6 +413,9 @@
   </si>
   <si>
     <t>(Kaduna Sept 2026) 4. Blackfly Lab App</t>
+  </si>
+  <si>
+    <t>allow_choice_duplicates</t>
   </si>
 </sst>
 </file>
@@ -3255,7 +3258,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="57.25" customWidth="1"/>
@@ -3264,7 +3267,7 @@
     <col min="4" max="4" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>123</v>
       </c>
@@ -3274,8 +3277,11 @@
       <c r="C1" s="2" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>129</v>
       </c>
@@ -3284,11 +3290,14 @@
       </c>
       <c r="C2" t="s">
         <v>126</v>
+      </c>
+      <c r="D2" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.69991251615088756" right="0.69991251615088756" top="0.74990626395218019" bottom="0.74990626395218019" header="0.51174154431801144" footer="0.51174154431801144"/>
-  <pageSetup paperSize="9"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>